--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484682_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484682_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. FOS CERVERA</t>
+          <t>M. ANTONI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7086</v>
+        <v>4.8523</v>
       </c>
       <c r="E2" t="n">
-        <v>8.464399999999999</v>
+        <v>5.0323</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.7558</v>
+        <v>-0.18</v>
       </c>
       <c r="G2" t="n">
-        <v>5.9405</v>
+        <v>2.539</v>
       </c>
       <c r="H2" t="n">
-        <v>7.2263</v>
+        <v>3.1931</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.2858</v>
+        <v>-0.6541</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8497</v>
+        <v>2.2692</v>
       </c>
       <c r="K2" t="n">
-        <v>7.0067</v>
+        <v>2.8269</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.157</v>
+        <v>-0.5577</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.2698</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2196</v>
+        <v>0.3662</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1288</v>
+        <v>-0.0964</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0995</v>
+        <v>-0.1833</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0995</v>
+        <v>0.9163</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7235</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5468</v>
+        <v>0.0905</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1767</v>
+        <v>-0.0992</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9554</v>
+        <v>1.5889</v>
       </c>
       <c r="W2" t="n">
-        <v>3.1674</v>
+        <v>2.8559</v>
       </c>
       <c r="X2" t="n">
-        <v>-4.1229</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. CORNEJO GONZALEZ</t>
+          <t>B. FOS CERVERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1199</v>
+        <v>4.7988</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3667</v>
+        <v>7.9014</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7533</v>
+        <v>-3.1026</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2826</v>
+        <v>5.9405</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4847</v>
+        <v>7.2263</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7979000000000001</v>
+        <v>-1.2858</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7259</v>
+        <v>5.8497</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6009</v>
+        <v>7.0067</v>
       </c>
       <c r="L3" t="n">
-        <v>0.125</v>
+        <v>-1.157</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5567</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1161</v>
+        <v>0.2196</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6729000000000001</v>
+        <v>-0.1288</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0995</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2828</v>
+        <v>1.0995</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5337</v>
+        <v>-0.1863</v>
       </c>
       <c r="T3" t="n">
-        <v>1.353</v>
+        <v>-0.0162</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1807</v>
+        <v>-0.1701</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.8796</v>
+        <v>-0.9554</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6127</v>
+        <v>3.1674</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.267</v>
+        <v>-4.1229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ANTONI RODRIGUEZ</t>
+          <t>M. CORNEJO GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6486</v>
+        <v>3.7105</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9773</v>
+        <v>3.1306</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3287</v>
+        <v>0.5799</v>
       </c>
       <c r="G4" t="n">
-        <v>2.539</v>
+        <v>5.2826</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1931</v>
+        <v>4.4847</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6541</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2692</v>
+        <v>4.7259</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8269</v>
+        <v>4.6009</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5577</v>
+        <v>0.125</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2698</v>
+        <v>0.5567</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3662</v>
+        <v>-0.1161</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0964</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1833</v>
+        <v>-1.0995</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2124</v>
+        <v>0.1242</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0355</v>
+        <v>0.1169</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2478</v>
+        <v>0.0073</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5889</v>
+        <v>-1.8796</v>
       </c>
       <c r="W4" t="n">
-        <v>2.8559</v>
+        <v>-0.6127</v>
       </c>
       <c r="X4" t="n">
         <v>-1.267</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. MARTINEZ TIBURCIO</t>
+          <t>A. GONZALEZ SOLER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8034</v>
+        <v>1.4279</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6258</v>
+        <v>1.3108</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1776</v>
+        <v>0.117</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9602000000000001</v>
+        <v>1.0764</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0849</v>
+        <v>1.817</v>
       </c>
       <c r="I5" t="n">
-        <v>1.045</v>
+        <v>-0.7406</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7359</v>
+        <v>1.2705</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5977</v>
+        <v>1.7865</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3336</v>
+        <v>-0.516</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2243</v>
+        <v>-0.1941</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5128</v>
+        <v>0.0305</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2885</v>
+        <v>-0.2246</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1652</v>
+        <v>-0.0596</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1101</v>
+        <v>0.0404</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2753</v>
+        <v>-0.0999</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3219</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GONZALEZ SOLER</t>
+          <t>I. MARTINEZ TIBURCIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6443</v>
+        <v>1.0919</v>
       </c>
       <c r="E6" t="n">
-        <v>0.775</v>
+        <v>0.9143</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1307</v>
+        <v>0.1776</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0764</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>1.817</v>
+        <v>-0.0849</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7406</v>
+        <v>1.045</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2705</v>
+        <v>0.7359</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7865</v>
+        <v>-0.5977</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.516</v>
+        <v>1.3336</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1941</v>
+        <v>0.2243</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0305</v>
+        <v>0.5128</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2246</v>
+        <v>-0.2885</v>
       </c>
       <c r="P6" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8431</v>
+        <v>0.4536</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4955</v>
+        <v>0.1784</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3477</v>
+        <v>0.2753</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3219</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0064</v>
+        <v>0.5949</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.443</v>
+        <v>-0.6187</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4365</v>
+        <v>1.2136</v>
       </c>
       <c r="G7" t="n">
         <v>1.0434</v>
@@ -1000,13 +1000,13 @@
         <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.301</v>
+        <v>-0.6997</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2111</v>
+        <v>-0.3869</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.3128</v>
       </c>
       <c r="V7" t="n">
         <v>1.9005</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.089</v>
+        <v>-0.9766</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7492</v>
+        <v>1.035</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8382</v>
+        <v>-2.0116</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0594</v>
@@ -1078,13 +1078,13 @@
         <v>0.9163</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6431</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0423</v>
+        <v>0.3281</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6008</v>
+        <v>0.4274</v>
       </c>
       <c r="V8" t="n">
         <v>-1.5889</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0027</v>
+        <v>-2.3098</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6798</v>
+        <v>-2.1851</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3229</v>
+        <v>-0.1247</v>
       </c>
       <c r="G9" t="n">
         <v>1.5952</v>
@@ -1156,13 +1156,13 @@
         <v>1.0995</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4983</v>
+        <v>-0.8054</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.276</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7276</v>
+        <v>-0.5294</v>
       </c>
       <c r="V9" t="n">
         <v>-1.267</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4184</v>
+        <v>-3.2776</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2402</v>
+        <v>-2.3224</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1782</v>
+        <v>-0.9553</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5504</v>
@@ -1234,13 +1234,13 @@
         <v>0.733</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.09039999999999999</v>
+        <v>0.0503</v>
       </c>
       <c r="T10" t="n">
-        <v>0.126</v>
+        <v>0.0438</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2164</v>
+        <v>0.0066</v>
       </c>
       <c r="V10" t="n">
         <v>0.3219</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6076</v>
+        <v>-3.8299</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3882</v>
+        <v>-0.6601</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2193</v>
+        <v>-3.1698</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4288</v>
@@ -1312,13 +1312,13 @@
         <v>0.9163</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2679</v>
+        <v>-0.4902</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2111</v>
+        <v>-0.483</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0567</v>
+        <v>-0.0072</v>
       </c>
       <c r="V11" t="n">
         <v>-1.9109</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.974</v>
+        <v>-5.4297</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2375</v>
+        <v>-3.7428</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7365</v>
+        <v>-1.6869</v>
       </c>
       <c r="G12" t="n">
         <v>-3.3187</v>
@@ -1390,13 +1390,13 @@
         <v>1.0995</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9564</v>
+        <v>-0.4121</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7903</v>
+        <v>-0.2956</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1661</v>
+        <v>-0.1165</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9658</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1732999999999993</v>
+        <v>0.6526999999999994</v>
       </c>
       <c r="E13" t="n">
-        <v>8.969699999999996</v>
+        <v>9.795299999999997</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.142899999999999</v>
+        <v>-9.142799999999999</v>
       </c>
       <c r="G13" t="n">
         <v>10.08</v>
@@ -1447,7 +1447,7 @@
         <v>16.2875</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.9594</v>
+        <v>-0.9594000000000005</v>
       </c>
       <c r="M13" t="n">
         <v>-5.248200000000001</v>
@@ -1468,13 +1468,13 @@
         <v>10.079</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.104</v>
+        <v>-1.2784</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4852</v>
+        <v>-0.6596</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6187</v>
+        <v>-0.6185000000000002</v>
       </c>
       <c r="V13" t="n">
         <v>-5.4001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.6349</v>
+        <v>4.6919</v>
       </c>
       <c r="E14" t="n">
-        <v>7.3738</v>
+        <v>4.7777</v>
       </c>
       <c r="F14" t="n">
-        <v>0.261</v>
+        <v>-0.0858</v>
       </c>
       <c r="G14" t="n">
         <v>-0.2086</v>
@@ -1546,13 +1546,13 @@
         <v>2.1991</v>
       </c>
       <c r="S14" t="n">
-        <v>4.3487</v>
+        <v>1.4057</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4948</v>
+        <v>0.8986</v>
       </c>
       <c r="U14" t="n">
-        <v>0.854</v>
+        <v>0.5071</v>
       </c>
       <c r="V14" t="n">
         <v>2.212</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7788</v>
+        <v>1.0036</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0081</v>
+        <v>3.4311</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2293</v>
+        <v>-2.4275</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7828000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>1.8326</v>
       </c>
       <c r="S16" t="n">
-        <v>1.352</v>
+        <v>0.5769</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9503</v>
+        <v>0.3733</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4018</v>
+        <v>0.2036</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6231</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. FAS MONROS</t>
+          <t>P. BAENA SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4334</v>
+        <v>0.3423</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7768</v>
+        <v>0.7822</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3434</v>
+        <v>-0.4399</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1658</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0378</v>
+        <v>-2.9459</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0321</v>
+        <v>2.78</v>
       </c>
       <c r="J18" t="n">
-        <v>0.356</v>
+        <v>1.7105</v>
       </c>
       <c r="K18" t="n">
-        <v>0.356</v>
+        <v>-0.3967</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.1072</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4259</v>
+        <v>-1.8763</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3938</v>
+        <v>-2.5492</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0321</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5034</v>
+        <v>-0.4082</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4208</v>
+        <v>-0.012</v>
       </c>
       <c r="U18" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.3961</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0124</v>
+        <v>0.2819</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3321</v>
+        <v>0.4282</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3445</v>
+        <v>-0.1463</v>
       </c>
       <c r="G19" t="n">
         <v>0.2046</v>
@@ -1936,13 +1936,13 @@
         <v>1.4661</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7668</v>
+        <v>-0.4725</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3318</v>
+        <v>-0.2356</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.435</v>
+        <v>-0.2368</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. BAENA SANCHEZ</t>
+          <t>R. FAS MONROS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3259</v>
+        <v>0.2688</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5639999999999999</v>
+        <v>0.4883</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7619</v>
+        <v>-0.2195</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1658</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.9459</v>
+        <v>-0.0378</v>
       </c>
       <c r="I20" t="n">
-        <v>2.78</v>
+        <v>-0.0321</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7105</v>
+        <v>0.356</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3967</v>
+        <v>0.356</v>
       </c>
       <c r="L20" t="n">
-        <v>2.1072</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8763</v>
+        <v>-0.4259</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.5492</v>
+        <v>-0.3938</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6729000000000001</v>
+        <v>-0.0321</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.0764</v>
+        <v>0.3388</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3582</v>
+        <v>0.1324</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7181999999999999</v>
+        <v>0.2064</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBANEZ</t>
+          <t>I. DE LA IGLESIA SANTAMARIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0466</v>
+        <v>-1.9392</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8832</v>
+        <v>-0.2645</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9298</v>
+        <v>-1.6747</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.3328</v>
+        <v>-1.1967</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.9062</v>
+        <v>-1.1741</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4266</v>
+        <v>-0.0226</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.22</v>
+        <v>0.1376</v>
       </c>
       <c r="K21" t="n">
-        <v>0.046</v>
+        <v>0.0959</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.266</v>
+        <v>0.0417</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.1128</v>
+        <v>-1.3342</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.9522</v>
+        <v>-1.27</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1606</v>
+        <v>-0.0643</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1833</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0158</v>
+        <v>0.3665</v>
       </c>
       <c r="S21" t="n">
-        <v>0.781</v>
+        <v>0.1188</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0694</v>
+        <v>-0.1297</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7116</v>
+        <v>0.2485</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3219</v>
+        <v>-0.3115</v>
       </c>
       <c r="W21" t="n">
-        <v>2.8663</v>
+        <v>0.6439</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.5444</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. DE LA IGLESIA SANTAMARIA</t>
+          <t>M. BERENGUER CASCO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0878</v>
+        <v>-2.0905</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2645</v>
+        <v>-0.7181999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8233</v>
+        <v>-1.3723</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1967</v>
+        <v>-5.007</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1741</v>
+        <v>-0.7762</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0226</v>
+        <v>-4.2308</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1376</v>
+        <v>-3.01</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0959</v>
+        <v>1.7333</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0417</v>
+        <v>-4.7433</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3342</v>
+        <v>-1.997</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.27</v>
+        <v>-2.5095</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0643</v>
+        <v>0.5125</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5498</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3665</v>
+        <v>2.3823</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0299</v>
+        <v>0.3984</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1297</v>
+        <v>-0.3883</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0998</v>
+        <v>0.7867</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3115</v>
+        <v>3.8009</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6439</v>
+        <v>6.3453</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.9554</v>
+        <v>-2.5444</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. BERENGUER CASCO</t>
+          <t>A. ORTEGA IBANEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.406</v>
+        <v>-2.3468</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2567</v>
+        <v>0.9794</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1493</v>
+        <v>-3.3262</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.007</v>
+        <v>-3.3328</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7762</v>
+        <v>-2.9062</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.2308</v>
+        <v>-0.4266</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.01</v>
+        <v>-0.22</v>
       </c>
       <c r="K23" t="n">
-        <v>1.7333</v>
+        <v>0.046</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.7433</v>
+        <v>-0.266</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.997</v>
+        <v>-3.1128</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.5095</v>
+        <v>-2.9522</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5125</v>
+        <v>-0.1606</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.2828</v>
+        <v>0.1833</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3823</v>
+        <v>2.0158</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9171</v>
+        <v>0.4808</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.9268</v>
+        <v>0.1656</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0097</v>
+        <v>0.3152</v>
       </c>
       <c r="V23" t="n">
-        <v>3.8009</v>
+        <v>0.3219</v>
       </c>
       <c r="W23" t="n">
-        <v>6.3453</v>
+        <v>2.8663</v>
       </c>
       <c r="X23" t="n">
         <v>-2.5444</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6207</v>
+        <v>-2.7683</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7046</v>
+        <v>-2.2238</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9161</v>
+        <v>-0.5445</v>
       </c>
       <c r="G24" t="n">
         <v>-2.3465</v>
@@ -2326,13 +2326,13 @@
         <v>0.733</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0909</v>
+        <v>-0.2385</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.0893</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5208</v>
+        <v>-0.1492</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1732999999999993</v>
+        <v>0.2692999999999994</v>
       </c>
       <c r="E25" t="n">
-        <v>10.4098</v>
+        <v>10.506</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.2366</v>
+        <v>-10.2367</v>
       </c>
       <c r="G25" t="n">
         <v>-10.08</v>
@@ -2404,16 +2404,16 @@
         <v>12.828</v>
       </c>
       <c r="S25" t="n">
-        <v>2.104000000000001</v>
+        <v>2.2002</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6186999999999996</v>
+        <v>0.7149999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4855</v>
+        <v>1.4854</v>
       </c>
       <c r="V25" t="n">
-        <v>5.4002</v>
+        <v>5.400200000000001</v>
       </c>
       <c r="W25" t="n">
         <v>14.6223</v>
